--- a/90101_REPORT_BOTTEGA_06-01-2026.xlsx
+++ b/90101_REPORT_BOTTEGA_06-01-2026.xlsx
@@ -9,12 +9,13 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
+    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="119">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -49,6 +50,39 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
+    <t>16:00 - 16:59</t>
+  </si>
+  <si>
+    <t>17:00 - 17:59</t>
+  </si>
+  <si>
+    <t>18:00 - 18:59</t>
+  </si>
+  <si>
+    <t>19:00 - 19:59</t>
+  </si>
+  <si>
+    <t>20:00 - 20:59</t>
+  </si>
+  <si>
+    <t>21:00 - 21:59</t>
+  </si>
+  <si>
+    <t>22:00 - 22:59</t>
+  </si>
+  <si>
+    <t>23:00 - 23:59</t>
+  </si>
+  <si>
+    <t>0:00 - 0:59</t>
+  </si>
+  <si>
+    <t>1:00 - 1:59</t>
+  </si>
+  <si>
+    <t>2:00 - 2:59</t>
+  </si>
+  <si>
     <t>TOTALE INCASSI 06/01/2026</t>
   </si>
   <si>
@@ -79,24 +113,24 @@
     <t>Bistecca Con Filetto 40-60 Gg</t>
   </si>
   <si>
+    <t>070002</t>
+  </si>
+  <si>
+    <t>Bistecca In Costata 40-60 Gg</t>
+  </si>
+  <si>
+    <t>50-004-011-002120</t>
+  </si>
+  <si>
+    <t>Controfiletto B.A.</t>
+  </si>
+  <si>
     <t>50-004-011-000590</t>
   </si>
   <si>
     <t>Filetto Bovino adulto</t>
   </si>
   <si>
-    <t>070002</t>
-  </si>
-  <si>
-    <t>Bistecca In Costata 40-60 Gg</t>
-  </si>
-  <si>
-    <t>50-004-011-002120</t>
-  </si>
-  <si>
-    <t>Controfiletto B.A.</t>
-  </si>
-  <si>
     <t>070066</t>
   </si>
   <si>
@@ -109,22 +143,52 @@
     <t>Punta Di Petto (Con Patate)</t>
   </si>
   <si>
+    <t>070005</t>
+  </si>
+  <si>
+    <t>Bistecca  Con Filetto 30-40 Gg</t>
+  </si>
+  <si>
+    <t>50-004-011-001480</t>
+  </si>
+  <si>
+    <t>Grigliata bovino</t>
+  </si>
+  <si>
+    <t>070001</t>
+  </si>
+  <si>
+    <t>Bistecca In Costata 30-40 Gg</t>
+  </si>
+  <si>
+    <t>50-004-011-001560</t>
+  </si>
+  <si>
+    <t>Pancetta porchettata</t>
+  </si>
+  <si>
+    <t>50-004-011-001300</t>
+  </si>
+  <si>
+    <t>Costine di suino</t>
+  </si>
+  <si>
+    <t>50-004-011-000600</t>
+  </si>
+  <si>
+    <t>Grigliata Mista</t>
+  </si>
+  <si>
     <t>070046</t>
   </si>
   <si>
     <t>Fiorentina 30-40 Gg (Asporto)</t>
   </si>
   <si>
-    <t>50-004-011-001480</t>
-  </si>
-  <si>
-    <t>Grigliata bovino</t>
-  </si>
-  <si>
-    <t>070005</t>
-  </si>
-  <si>
-    <t>Bistecca  Con Filetto 30-40 Gg</t>
+    <t>50-004-011-000860</t>
+  </si>
+  <si>
+    <t>Patate Al Forno</t>
   </si>
   <si>
     <t>070047</t>
@@ -133,42 +197,18 @@
     <t>Fiorenita 20-30 Gg (Da Cucinare)</t>
   </si>
   <si>
+    <t>50-004-011-001310</t>
+  </si>
+  <si>
+    <t>Hamburger di B.A. con patate</t>
+  </si>
+  <si>
     <t>070045</t>
   </si>
   <si>
     <t>Fiorentina 20-30 (Asporto)</t>
   </si>
   <si>
-    <t>50-004-011-001300</t>
-  </si>
-  <si>
-    <t>Costine di suino</t>
-  </si>
-  <si>
-    <t>50-004-011-000860</t>
-  </si>
-  <si>
-    <t>Patate Al Forno</t>
-  </si>
-  <si>
-    <t>50-004-011-001560</t>
-  </si>
-  <si>
-    <t>Pancetta porchettata</t>
-  </si>
-  <si>
-    <t>50-004-011-000600</t>
-  </si>
-  <si>
-    <t>Grigliata Mista</t>
-  </si>
-  <si>
-    <t>50-004-011-001310</t>
-  </si>
-  <si>
-    <t>Hamburger di B.A. con patate</t>
-  </si>
-  <si>
     <t>50-004-011-001370</t>
   </si>
   <si>
@@ -181,6 +221,24 @@
     <t>Etrusca Marinata Birra (Con Patate)</t>
   </si>
   <si>
+    <t>50-004-011-000700</t>
+  </si>
+  <si>
+    <t>Tagliata Pollo</t>
+  </si>
+  <si>
+    <t>50-004-011-001500</t>
+  </si>
+  <si>
+    <t>Salsiccia cinta</t>
+  </si>
+  <si>
+    <t>50-004-011-001390</t>
+  </si>
+  <si>
+    <t>Tomahawk suino</t>
+  </si>
+  <si>
     <t>50-004-011-000660</t>
   </si>
   <si>
@@ -193,10 +251,22 @@
     <t>Costata 30-40 Gg (Asporto)</t>
   </si>
   <si>
-    <t>50-004-011-001500</t>
-  </si>
-  <si>
-    <t>Salsiccia cinta</t>
+    <t>50-004-011-000670</t>
+  </si>
+  <si>
+    <t>Spiedini Misti</t>
+  </si>
+  <si>
+    <t>50-004-011-000850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insalata Mista </t>
+  </si>
+  <si>
+    <t>50-004-011-001660</t>
+  </si>
+  <si>
+    <t>Riso</t>
   </si>
   <si>
     <t>50-004-011-000610</t>
@@ -205,28 +275,16 @@
     <t>Grigliata Mista Xxl</t>
   </si>
   <si>
-    <t>50-004-011-000670</t>
-  </si>
-  <si>
-    <t>Spiedini Misti</t>
-  </si>
-  <si>
-    <t>50-004-011-000700</t>
-  </si>
-  <si>
-    <t>Tagliata Pollo</t>
-  </si>
-  <si>
-    <t>50-004-011-001660</t>
-  </si>
-  <si>
-    <t>Riso</t>
-  </si>
-  <si>
-    <t>50-004-011-000850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insalata Mista </t>
+    <t>070044</t>
+  </si>
+  <si>
+    <t>Filetto B.A.</t>
+  </si>
+  <si>
+    <t>070057</t>
+  </si>
+  <si>
+    <t>Polletto</t>
   </si>
   <si>
     <t>50-004-011-002270</t>
@@ -241,10 +299,19 @@
     <t>Salsiccia Di Cinta</t>
   </si>
   <si>
+    <t>50-004-011-000560</t>
+  </si>
+  <si>
+    <t>Arrosticini Di Pecora</t>
+  </si>
+  <si>
     <t>070035</t>
   </si>
   <si>
-    <t>Arrosticini Di Pecora</t>
+    <t>50-004-011-000620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamburger Di B.A. </t>
   </si>
   <si>
     <t>070043</t>
@@ -265,6 +332,18 @@
     <t>Contorno Del Giorno</t>
   </si>
   <si>
+    <t>070053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamburger Cinta </t>
+  </si>
+  <si>
+    <t>50-004-011-888888</t>
+  </si>
+  <si>
+    <t>Shopper BIO</t>
+  </si>
+  <si>
     <t>TOTALE GRUPPO</t>
   </si>
   <si>
@@ -278,6 +357,21 @@
   </si>
   <si>
     <t>12:00-15:59</t>
+  </si>
+  <si>
+    <t>16:00-18:59</t>
+  </si>
+  <si>
+    <t>19:00-02:59</t>
+  </si>
+  <si>
+    <t>06/01/2026</t>
+  </si>
+  <si>
+    <t>VAR %</t>
+  </si>
+  <si>
+    <t>06/01/2025</t>
   </si>
 </sst>
 </file>
@@ -415,7 +509,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -428,13 +522,27 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -522,27 +630,115 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="1">
+      <c r="A11" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="1">
-        <v>2848.61</v>
+      <c r="B11" t="n" s="5">
+        <v>280.8636</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="1">
+      <c r="A12" t="s" s="4">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="1">
-        <v>4047.57</v>
+      <c r="B12" t="n" s="7">
+        <v>123.3635</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="1">
+      <c r="A13" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="1">
-        <v>-29.62</v>
+      <c r="B13" t="n" s="5">
+        <v>305.7106</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="4">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n" s="7">
+        <v>383.7272</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n" s="5">
+        <v>157.3093</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="4">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n" s="7">
+        <v>60.3091</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="4">
+        <v>18</v>
+      </c>
+      <c r="B18" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="B20" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B21" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="B22" t="n" s="1">
+        <v>4159.89</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>23</v>
+      </c>
+      <c r="B23" t="n" s="1">
+        <v>6296.54</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B24" t="n" s="1">
+        <v>-33.93</v>
       </c>
     </row>
   </sheetData>
@@ -552,7 +748,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -564,577 +760,713 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>353.2727</v>
+        <v>417.2272</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>5.8</v>
+        <v>6.85</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>12.4</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>220.0</v>
+        <v>276.2909</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>11.0</v>
+        <v>5.33</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>7.72</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>200.6364</v>
+        <v>272.7272</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>3.87</v>
+        <v>15.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>7.04</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>181.8182</v>
+        <v>260.0</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>6.38</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n" s="7">
-        <v>178.1818</v>
+        <v>236.2727</v>
       </c>
       <c r="D6" t="n" s="7">
-        <v>4.0</v>
+        <v>5.3</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>6.26</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n" s="5">
-        <v>162.7273</v>
+        <v>227.8182</v>
       </c>
       <c r="D7" t="n" s="5">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>5.71</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n" s="7">
-        <v>158.7273</v>
+        <v>214.3364</v>
       </c>
       <c r="D8" t="n" s="7">
-        <v>3.29</v>
+        <v>3.69</v>
       </c>
       <c r="E8" t="n" s="7">
-        <v>5.57</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n" s="5">
-        <v>150.0</v>
+        <v>210.0</v>
       </c>
       <c r="D9" t="n" s="5">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="E9" t="n" s="5">
-        <v>5.27</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n" s="7">
-        <v>149.291</v>
+        <v>205.5273</v>
       </c>
       <c r="D10" t="n" s="7">
-        <v>2.57</v>
+        <v>4.18</v>
       </c>
       <c r="E10" t="n" s="7">
-        <v>5.24</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n" s="5">
-        <v>141.9091</v>
+        <v>179.9999</v>
       </c>
       <c r="D11" t="n" s="5">
-        <v>2.65</v>
+        <v>11.0</v>
       </c>
       <c r="E11" t="n" s="5">
-        <v>4.98</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C12" t="n" s="7">
-        <v>110.9182</v>
+        <v>164.2729</v>
       </c>
       <c r="D12" t="n" s="7">
-        <v>2.49</v>
+        <v>13.0</v>
       </c>
       <c r="E12" t="n" s="7">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n" s="5">
-        <v>101.091</v>
+        <v>163.6362</v>
       </c>
       <c r="D13" t="n" s="5">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="E13" t="n" s="5">
-        <v>3.55</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C14" t="n" s="7">
-        <v>100.0</v>
+        <v>158.7273</v>
       </c>
       <c r="D14" t="n" s="7">
-        <v>22.0</v>
+        <v>3.29</v>
       </c>
       <c r="E14" t="n" s="7">
-        <v>3.51</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C15" t="n" s="5">
-        <v>98.1818</v>
+        <v>150.0</v>
       </c>
       <c r="D15" t="n" s="5">
-        <v>6.0</v>
+        <v>33.0</v>
       </c>
       <c r="E15" t="n" s="5">
-        <v>3.45</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C16" t="n" s="7">
-        <v>98.1817</v>
+        <v>141.9091</v>
       </c>
       <c r="D16" t="n" s="7">
-        <v>6.0</v>
+        <v>2.65</v>
       </c>
       <c r="E16" t="n" s="7">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C17" t="n" s="5">
-        <v>63.1818</v>
+        <v>126.3637</v>
       </c>
       <c r="D17" t="n" s="5">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="E17" t="n" s="5">
-        <v>2.22</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C18" t="n" s="7">
-        <v>60.0</v>
+        <v>110.9182</v>
       </c>
       <c r="D18" t="n" s="7">
-        <v>11.0</v>
+        <v>2.49</v>
       </c>
       <c r="E18" t="n" s="7">
-        <v>2.11</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C19" t="n" s="5">
-        <v>49.0909</v>
+        <v>97.0907</v>
       </c>
       <c r="D19" t="n" s="5">
-        <v>3.0</v>
+        <v>18.0</v>
       </c>
       <c r="E19" t="n" s="5">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C20" t="n" s="7">
-        <v>46.9091</v>
+        <v>65.4545</v>
       </c>
       <c r="D20" t="n" s="7">
         <v>4.0</v>
       </c>
       <c r="E20" t="n" s="7">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C21" t="n" s="5">
-        <v>38.8364</v>
+        <v>58.6364</v>
       </c>
       <c r="D21" t="n" s="5">
-        <v>1.19</v>
+        <v>5.0</v>
       </c>
       <c r="E21" t="n" s="5">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C22" t="n" s="7">
-        <v>25.2728</v>
+        <v>50.5455</v>
       </c>
       <c r="D22" t="n" s="7">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E22" t="n" s="7">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C23" t="n" s="5">
-        <v>24.4545</v>
+        <v>49.0909</v>
       </c>
       <c r="D23" t="n" s="5">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E23" t="n" s="5">
-        <v>0.86</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="4">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C24" t="n" s="7">
-        <v>23.4546</v>
+        <v>46.9091</v>
       </c>
       <c r="D24" t="n" s="7">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E24" t="n" s="7">
-        <v>0.82</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C25" t="n" s="5">
-        <v>23.4546</v>
+        <v>38.8364</v>
       </c>
       <c r="D25" t="n" s="5">
-        <v>2.0</v>
+        <v>1.19</v>
       </c>
       <c r="E25" t="n" s="5">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="4">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s" s="4">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C26" t="n" s="7">
-        <v>22.7273</v>
+        <v>35.1819</v>
       </c>
       <c r="D26" t="n" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="E26" t="n" s="7">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C27" t="n" s="5">
-        <v>13.6364</v>
+        <v>31.8184</v>
       </c>
       <c r="D27" t="n" s="5">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="E27" t="n" s="5">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="4">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B28" t="s" s="4">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C28" t="n" s="7">
-        <v>12.6364</v>
+        <v>31.8183</v>
       </c>
       <c r="D28" t="n" s="7">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="E28" t="n" s="7">
-        <v>0.44</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C29" t="n" s="5">
-        <v>11.7727</v>
+        <v>24.4545</v>
       </c>
       <c r="D29" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="E29" t="n" s="5">
-        <v>0.41</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="4">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s" s="4">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C30" t="n" s="7">
-        <v>9.0909</v>
+        <v>22.3091</v>
       </c>
       <c r="D30" t="n" s="7">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="E30" t="n" s="7">
-        <v>0.32</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C31" t="n" s="5">
-        <v>7.6364</v>
+        <v>13.8727</v>
       </c>
       <c r="D31" t="n" s="5">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="E31" t="n" s="5">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="4">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B32" t="s" s="4">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C32" t="n" s="7">
-        <v>6.0637</v>
+        <v>12.6364</v>
       </c>
       <c r="D32" t="n" s="7">
-        <v>0.6</v>
+        <v>1.0</v>
       </c>
       <c r="E32" t="n" s="7">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C33" t="n" s="5">
+        <v>11.7727</v>
+      </c>
+      <c r="D33" t="n" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E33" t="n" s="5">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="4">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s" s="4">
+        <v>95</v>
+      </c>
+      <c r="C34" t="n" s="7">
+        <v>10.9091</v>
+      </c>
+      <c r="D34" t="n" s="7">
+        <v>10.0</v>
+      </c>
+      <c r="E34" t="n" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C35" t="n" s="5">
+        <v>9.0909</v>
+      </c>
+      <c r="D35" t="n" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E35" t="n" s="5">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="4">
+        <v>97</v>
+      </c>
+      <c r="B36" t="s" s="4">
+        <v>98</v>
+      </c>
+      <c r="C36" t="n" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="D36" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E36" t="n" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="C37" t="n" s="5">
+        <v>7.6364</v>
+      </c>
+      <c r="D37" t="n" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="E37" t="n" s="5">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="4">
+        <v>101</v>
+      </c>
+      <c r="B38" t="s" s="4">
+        <v>102</v>
+      </c>
+      <c r="C38" t="n" s="7">
+        <v>6.0637</v>
+      </c>
+      <c r="D38" t="n" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="E38" t="n" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="C39" t="n" s="5">
         <v>5.4545</v>
       </c>
-      <c r="D33" t="n" s="5">
+      <c r="D39" t="n" s="5">
         <v>1.0</v>
       </c>
-      <c r="E33" t="n" s="5">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="1">
-        <v>83</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" t="n" s="1">
-        <v>2848.61</v>
-      </c>
-      <c r="D34" t="n" s="1">
-        <v>145.66</v>
-      </c>
-      <c r="E34" t="n" s="1">
+      <c r="E39" t="n" s="5">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="4">
+        <v>105</v>
+      </c>
+      <c r="B40" t="s" s="4">
+        <v>106</v>
+      </c>
+      <c r="C40" t="n" s="7">
+        <v>4.3818</v>
+      </c>
+      <c r="D40" t="n" s="7">
+        <v>0.22</v>
+      </c>
+      <c r="E40" t="n" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C41" t="n" s="5">
+        <v>0.9017</v>
+      </c>
+      <c r="D41" t="n" s="5">
+        <v>11.0</v>
+      </c>
+      <c r="E41" t="n" s="5">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="1">
+        <v>109</v>
+      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" t="n" s="1">
+        <v>4159.89</v>
+      </c>
+      <c r="D42" t="n" s="1">
+        <v>244.81</v>
+      </c>
+      <c r="E42" t="n" s="1">
         <v>100.0</v>
       </c>
     </row>
@@ -1145,7 +1477,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -1156,13 +1488,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -1170,15 +1502,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>84</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C3" t="n" s="5">
         <v>2.0</v>
@@ -1189,10 +1521,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C4" t="n" s="7">
         <v>2.0</v>
@@ -1203,10 +1535,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C5" t="n" s="5">
         <v>1.9</v>
@@ -1217,10 +1549,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>1.6</v>
@@ -1231,10 +1563,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C7" t="n" s="5">
         <v>1.25</v>
@@ -1245,10 +1577,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n" s="7">
         <v>1.2</v>
@@ -1259,10 +1591,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C9" t="n" s="5">
         <v>1.0</v>
@@ -1273,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n" s="7">
         <v>1.0</v>
@@ -1287,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>1.0</v>
@@ -1301,10 +1633,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>0.4</v>
@@ -1315,10 +1647,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="1">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C13" t="n" s="1">
         <v>13.35</v>
@@ -1330,15 +1662,15 @@
     <row r="14"/>
     <row r="15">
       <c r="A15" t="s" s="1">
-        <v>87</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C16" t="n" s="7">
         <v>22.0</v>
@@ -1349,10 +1681,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C17" t="n" s="5">
         <v>11.0</v>
@@ -1363,10 +1695,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C18" t="n" s="7">
         <v>10.0</v>
@@ -1377,10 +1709,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C19" t="n" s="5">
         <v>9.0</v>
@@ -1391,10 +1723,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C20" t="n" s="7">
         <v>9.0</v>
@@ -1405,10 +1737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C21" t="n" s="5">
         <v>8.0</v>
@@ -1419,10 +1751,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C22" t="n" s="7">
         <v>5.8</v>
@@ -1433,10 +1765,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C23" t="n" s="5">
         <v>5.0</v>
@@ -1447,10 +1779,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="4">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C24" t="n" s="7">
         <v>5.0</v>
@@ -1461,10 +1793,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C25" t="n" s="5">
         <v>5.0</v>
@@ -1475,10 +1807,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="4">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s" s="4">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C26" t="n" s="7">
         <v>5.0</v>
@@ -1489,10 +1821,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C27" t="n" s="5">
         <v>4.0</v>
@@ -1503,10 +1835,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="4">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B28" t="s" s="4">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C28" t="n" s="7">
         <v>4.0</v>
@@ -1517,10 +1849,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C29" t="n" s="5">
         <v>3.87</v>
@@ -1531,10 +1863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="4">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s" s="4">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C30" t="n" s="7">
         <v>3.0</v>
@@ -1545,10 +1877,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C31" t="n" s="5">
         <v>3.0</v>
@@ -1559,10 +1891,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="4">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B32" t="s" s="4">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C32" t="n" s="7">
         <v>2.8</v>
@@ -1573,10 +1905,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C33" t="n" s="5">
         <v>2.65</v>
@@ -1587,10 +1919,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="4">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B34" t="s" s="4">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C34" t="n" s="7">
         <v>2.0</v>
@@ -1601,10 +1933,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C35" t="n" s="5">
         <v>2.0</v>
@@ -1615,10 +1947,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="4">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s" s="4">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C36" t="n" s="7">
         <v>1.39</v>
@@ -1629,10 +1961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C37" t="n" s="5">
         <v>1.32</v>
@@ -1643,10 +1975,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="4">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B38" t="s" s="4">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C38" t="n" s="7">
         <v>1.19</v>
@@ -1657,10 +1989,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C39" t="n" s="5">
         <v>1.0</v>
@@ -1671,10 +2003,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="4">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s" s="4">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="C40" t="n" s="7">
         <v>1.0</v>
@@ -1685,10 +2017,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C41" t="n" s="5">
         <v>1.0</v>
@@ -1699,10 +2031,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="4">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="B42" t="s" s="4">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C42" t="n" s="7">
         <v>1.0</v>
@@ -1713,10 +2045,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C43" t="n" s="5">
         <v>0.89</v>
@@ -1727,10 +2059,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="4">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="B44" t="s" s="4">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C44" t="n" s="7">
         <v>0.6</v>
@@ -1741,10 +2073,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C45" t="n" s="5">
         <v>0.5</v>
@@ -1755,10 +2087,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="4">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="B46" t="s" s="4">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C46" t="n" s="7">
         <v>0.3</v>
@@ -1769,10 +2101,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="1">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C47" t="n" s="1">
         <v>132.31</v>
@@ -1782,13 +2114,655 @@
       </c>
     </row>
     <row r="48"/>
+    <row r="49">
+      <c r="A49" t="s" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="4">
+        <v>107</v>
+      </c>
+      <c r="B50" t="s" s="4">
+        <v>108</v>
+      </c>
+      <c r="C50" t="n" s="7">
+        <v>10.0</v>
+      </c>
+      <c r="D50" t="n" s="7">
+        <v>0.8197</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="C51" t="n" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="D51" t="n" s="5">
+        <v>36.3636</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="4">
+        <v>60</v>
+      </c>
+      <c r="B52" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="C52" t="n" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="D52" t="n" s="7">
+        <v>63.1819</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C53" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="D53" t="n" s="5">
+        <v>49.0909</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="B54" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C54" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D54" t="n" s="7">
+        <v>48.8182</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C55" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="D55" t="n" s="5">
+        <v>37.9091</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="4">
+        <v>64</v>
+      </c>
+      <c r="B56" t="s" s="4">
+        <v>65</v>
+      </c>
+      <c r="C56" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D56" t="n" s="7">
+        <v>16.3635</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C57" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D57" t="n" s="5">
+        <v>60.0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="B58" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="C58" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D58" t="n" s="7">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="C59" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D59" t="n" s="5">
+        <v>36.3636</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="4">
+        <v>52</v>
+      </c>
+      <c r="B60" t="s" s="4">
+        <v>53</v>
+      </c>
+      <c r="C60" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D60" t="n" s="7">
+        <v>32.7272</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C61" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D61" t="n" s="5">
+        <v>32.7272</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="4">
+        <v>80</v>
+      </c>
+      <c r="B62" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="C62" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D62" t="n" s="7">
+        <v>9.091</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C63" t="n" s="5">
+        <v>1.49</v>
+      </c>
+      <c r="D63" t="n" s="5">
+        <v>73.3637</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="B64" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="C64" t="n" s="7">
+        <v>1.3</v>
+      </c>
+      <c r="D64" t="n" s="7">
+        <v>58.0909</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C65" t="n" s="5">
+        <v>1.12</v>
+      </c>
+      <c r="D65" t="n" s="5">
+        <v>65.0454</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="4">
+        <v>66</v>
+      </c>
+      <c r="B66" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="C66" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D66" t="n" s="7">
+        <v>16.3636</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C67" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D67" t="n" s="5">
+        <v>11.7273</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="4">
+        <v>97</v>
+      </c>
+      <c r="B68" t="s" s="4">
+        <v>98</v>
+      </c>
+      <c r="C68" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D68" t="n" s="7">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C69" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D69" t="n" s="5">
+        <v>4.5455</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="4">
+        <v>88</v>
+      </c>
+      <c r="B70" t="s" s="4">
+        <v>89</v>
+      </c>
+      <c r="C70" t="n" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="D70" t="n" s="7">
+        <v>3.9636</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="C71" t="n" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="D71" t="n" s="5">
+        <v>4.3818</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="1">
+        <v>111</v>
+      </c>
+      <c r="B72" t="s" s="4">
+        <v>112</v>
+      </c>
+      <c r="C72" t="n" s="1">
+        <v>55.53</v>
+      </c>
+      <c r="D72" t="n" s="1">
+        <v>709.94</v>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74">
+      <c r="A74" t="s" s="1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C75" t="n" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="D75" t="n" s="5">
+        <v>10.9091</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="4">
+        <v>64</v>
+      </c>
+      <c r="B76" t="s" s="4">
+        <v>65</v>
+      </c>
+      <c r="C76" t="n" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="D76" t="n" s="7">
+        <v>20.7272</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="C77" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="D77" t="n" s="5">
+        <v>54.5454</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="B78" t="s" s="4">
+        <v>49</v>
+      </c>
+      <c r="C78" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D78" t="n" s="7">
+        <v>49.0909</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="C79" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="D79" t="n" s="5">
+        <v>35.1818</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="4">
+        <v>56</v>
+      </c>
+      <c r="B80" t="s" s="4">
+        <v>57</v>
+      </c>
+      <c r="C80" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D80" t="n" s="7">
+        <v>13.6364</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C81" t="n" s="5">
+        <v>2.69</v>
+      </c>
+      <c r="D81" t="n" s="5">
+        <v>132.1636</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="4">
+        <v>52</v>
+      </c>
+      <c r="B82" t="s" s="4">
+        <v>53</v>
+      </c>
+      <c r="C82" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D82" t="n" s="7">
+        <v>32.7273</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C83" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D83" t="n" s="5">
+        <v>25.2728</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="4">
+        <v>70</v>
+      </c>
+      <c r="B84" t="s" s="4">
+        <v>71</v>
+      </c>
+      <c r="C84" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D84" t="n" s="7">
+        <v>25.2727</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C85" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D85" t="n" s="5">
+        <v>9.091</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="4">
+        <v>32</v>
+      </c>
+      <c r="B86" t="s" s="4">
+        <v>33</v>
+      </c>
+      <c r="C86" t="n" s="7">
+        <v>1.46</v>
+      </c>
+      <c r="D86" t="n" s="7">
+        <v>75.6545</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C87" t="n" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="D87" t="n" s="5">
+        <v>63.9545</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="B88" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C88" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D88" t="n" s="7">
+        <v>16.2727</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C89" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D89" t="n" s="5">
+        <v>9.9091</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="4">
+        <v>82</v>
+      </c>
+      <c r="B90" t="s" s="4">
+        <v>83</v>
+      </c>
+      <c r="C90" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D90" t="n" s="7">
+        <v>4.5455</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C91" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D91" t="n" s="5">
+        <v>0.082</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="4">
+        <v>86</v>
+      </c>
+      <c r="B92" t="s" s="4">
+        <v>87</v>
+      </c>
+      <c r="C92" t="n" s="7">
+        <v>0.42</v>
+      </c>
+      <c r="D92" t="n" s="7">
+        <v>22.3091</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="1">
+        <v>111</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C93" t="n" s="1">
+        <v>43.62</v>
+      </c>
+      <c r="D93" t="n" s="1">
+        <v>601.35</v>
+      </c>
+    </row>
+    <row r="94"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A93:B93"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>116</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>117</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="9">
+        <v>5656.0</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <f>(A2-C2)/C2</f>
+        <v>0.0</v>
+      </c>
+      <c r="C2" t="n" s="9">
+        <v>6939.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>